--- a/data-raw/desc_funcao.xlsx
+++ b/data-raw/desc_funcao.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26911"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\2.Programação e Normas\2023\PPAG 2023 e LOA 2023\Tabelas de Apoio - geração dos volumes 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B673155B7E1682D92CC8B3728F1F5C845B914187" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21840" windowHeight="7815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21840" windowHeight="7815"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$B$30</definedName>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -138,8 +137,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,16 +448,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -474,7 +472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -482,7 +480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -490,7 +488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -498,7 +496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -506,7 +504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -514,7 +512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -522,7 +520,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -530,7 +528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -538,7 +536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -546,7 +544,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -554,7 +552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -562,7 +560,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -570,7 +568,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -578,7 +576,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -586,7 +584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -594,7 +592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -602,7 +600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -610,7 +608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -618,7 +616,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -626,7 +624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -634,7 +632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -642,7 +640,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -650,7 +648,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -658,7 +656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -666,7 +664,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -674,7 +672,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -682,7 +680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -690,7 +688,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>99</v>
       </c>
@@ -705,8 +703,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -965,41 +990,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349A8D6F-7AA9-451D-8D84-87A7D6825CEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A826D78-3D96-4E69-A209-AF396A472B46}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27DD4324-C7F1-4A7D-8D71-A7008EDB9033}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27DD4324-C7F1-4A7D-8D71-A7008EDB9033}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A826D78-3D96-4E69-A209-AF396A472B46}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BEF89E1-A519-4263-A1AB-EFA662F2E82F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>